--- a/sample_data/organization_usage_update_template.xlsx
+++ b/sample_data/organization_usage_update_template.xlsx
@@ -427,16 +427,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,20 +460,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ManufacturingCalendarId</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DefaultWorkMethod</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>EnableProcessManufacturingFlag</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>ManufacturingPlantFlag</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MaintenanceEnabledFlag</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ContractManufacturingFlag</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>IntegratedSystemType</t>
         </is>
@@ -488,16 +506,21 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -507,6 +530,9 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -516,6 +542,9 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -528,13 +557,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -748,114 +777,114 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Additional Usages</t>
+          <t>Plant Parameters Helper</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Organization is a manufacturing plant</t>
+          <t>Manufacturing Calendar ID</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ManufacturingPlantFlag</t>
+          <t>ManufacturingCalendarId</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ManufacturingPlantFlag</t>
+          <t>ManufacturingCalendarId</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Inventory Organization parent field</t>
+          <t>Schedules / invOrgParameters.ScheduleId</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Centang jika inventory organization dipakai sebagai manufacturing plant.</t>
+          <t>Dipakai app untuk membuat child plantParameters jika ManufacturingPlantFlag atau MaintenanceEnabledFlag dicentang. Jika kosong, runner akan coba memakai invOrgParameters.ScheduleId dari Oracle.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Additional Usages</t>
+          <t>Plant Parameters Helper</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Organization performs maintenance activities</t>
+          <t>Default Work Method</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MaintenanceEnabledFlag</t>
+          <t>DefaultWorkMethod</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MaintenanceEnabledFlag</t>
+          <t>DefaultWorkMethod</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Inventory Organization parent field</t>
+          <t>Plant parameters</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Centang jika organization menjalankan maintenance activities.</t>
+          <t>Opsional. Ikut dikirim saat create plantParameters jika diisi. Contoh value harus sesuai setup Oracle, misalnya DISCRETE_MANUFACTURING/PROCESS_MANUFACTURING jika valid di instance.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Additional Usages</t>
+          <t>Plant Parameters Helper</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Organization represents a contract manufacturer</t>
+          <t>Enable Process Manufacturing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ContractManufacturingFlag</t>
+          <t>EnableProcessManufacturingFlag</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ContractManufacturingFlag</t>
+          <t>EnableProcessManufacturingFlag</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -867,19 +896,19 @@
         <v>0</v>
       </c>
       <c r="G7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Inventory Organization parent field</t>
+          <t>Plant parameters</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Centang jika organization merepresentasikan contract manufacturer.</t>
+          <t>Opsional. Ikut dikirim saat create plantParameters jika diisi.</t>
         </is>
       </c>
     </row>
@@ -891,22 +920,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Integrated System Type</t>
+          <t>Organization is a manufacturing plant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IntegratedSystemType</t>
+          <t>ManufacturingPlantFlag</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IntegratedSystemType</t>
+          <t>ManufacturingPlantFlag</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -920,10 +949,148 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
+          <t>Inventory Organization parent field</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Centang jika inventory organization dipakai sebagai manufacturing plant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Additional Usages</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Organization performs maintenance activities</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MaintenanceEnabledFlag</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MaintenanceEnabledFlag</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Inventory Organization parent field</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Centang jika organization menjalankan maintenance activities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Additional Usages</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Organization represents a contract manufacturer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ContractManufacturingFlag</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ContractManufacturingFlag</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Inventory Organization parent field</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Centang jika organization merepresentasikan contract manufacturer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Additional Usages</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Integrated System Type</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IntegratedSystemType</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IntegratedSystemType</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>Ambil dari existing IO/current value jika tersedia.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Integrated System Type. Kosongkan jika tidak ingin di-update. Isi dengan value/code yang memang valid di instance Oracle.</t>
         </is>

--- a/sample_data/organization_usage_update_template.xlsx
+++ b/sample_data/organization_usage_update_template.xlsx
@@ -427,19 +427,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,30 +467,40 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>DefSupplySubinv</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>DefCompltnSubinv</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>DefaultWorkMethod</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>EnableProcessManufacturingFlag</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ManufacturingPlantFlag</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MaintenanceEnabledFlag</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ContractManufacturingFlag</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>IntegratedSystemType</t>
         </is>
@@ -505,22 +517,40 @@
           <t>IO Test 01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
+      <c r="C2" t="n">
+        <v>300000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>300000047225452</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RAW</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FG</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Oracle Inventory Management</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -533,6 +563,8 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -545,6 +577,8 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -557,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -570,7 +604,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="53" customWidth="1" min="11" max="11"/>
+    <col width="58" customWidth="1" min="11" max="11"/>
     <col width="58" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -828,17 +862,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Default Work Method</t>
+          <t>Default Supply Subinventory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DefaultWorkMethod</t>
+          <t>DefSupplySubinv</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DefaultWorkMethod</t>
+          <t>DefSupplySubinv</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -857,12 +891,12 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Plant parameters</t>
+          <t>Isi dengan SecondaryInventoryName dari subinventory yang sudah dibuat di IO tersebut.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Opsional. Ikut dikirim saat create plantParameters jika diisi. Contoh value harus sesuai setup Oracle, misalnya DISCRETE_MANUFACTURING/PROCESS_MANUFACTURING jika valid di instance.</t>
+          <t>Kode/nama subinventory default supply untuk create plantParameters. Wajib diisi jika ManufacturingPlantFlag atau MaintenanceEnabledFlag dicentang.</t>
         </is>
       </c>
     </row>
@@ -874,22 +908,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Enable Process Manufacturing</t>
+          <t>Default Completion Subinventory</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EnableProcessManufacturingFlag</t>
+          <t>DefCompltnSubinv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EnableProcessManufacturingFlag</t>
+          <t>DefCompltnSubinv</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -903,80 +937,80 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Plant parameters</t>
+          <t>Isi dengan SecondaryInventoryName dari subinventory yang sudah dibuat di IO tersebut.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Opsional. Ikut dikirim saat create plantParameters jika diisi.</t>
+          <t>Kode/nama subinventory default completion untuk create plantParameters. Wajib diisi jika ManufacturingPlantFlag atau MaintenanceEnabledFlag dicentang.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Additional Usages</t>
+          <t>Plant Parameters Helper</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Organization is a manufacturing plant</t>
+          <t>Default Work Method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ManufacturingPlantFlag</t>
+          <t>DefaultWorkMethod</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ManufacturingPlantFlag</t>
+          <t>DefaultWorkMethod</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
       <c r="G8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Inventory Organization parent field</t>
+          <t>Plant parameters</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Centang jika inventory organization dipakai sebagai manufacturing plant.</t>
+          <t>Opsional. Ikut dikirim saat create plantParameters jika diisi. Contoh value harus sesuai setup Oracle, misalnya DISCRETE_MANUFACTURING/PROCESS_MANUFACTURING jika valid di instance.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Additional Usages</t>
+          <t>Plant Parameters Helper</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Organization performs maintenance activities</t>
+          <t>Enable Process Manufacturing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MaintenanceEnabledFlag</t>
+          <t>EnableProcessManufacturingFlag</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MaintenanceEnabledFlag</t>
+          <t>EnableProcessManufacturingFlag</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -988,19 +1022,19 @@
         <v>0</v>
       </c>
       <c r="G9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Inventory Organization parent field</t>
+          <t>Plant parameters</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Centang jika organization menjalankan maintenance activities.</t>
+          <t>Opsional. Ikut dikirim saat create plantParameters jika diisi.</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1046,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Organization represents a contract manufacturer</t>
+          <t>Organization is a manufacturing plant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ContractManufacturingFlag</t>
+          <t>ManufacturingPlantFlag</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ContractManufacturingFlag</t>
+          <t>ManufacturingPlantFlag</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1046,7 +1080,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Centang jika organization merepresentasikan contract manufacturer.</t>
+          <t>Centang jika inventory organization dipakai sebagai manufacturing plant.</t>
         </is>
       </c>
     </row>
@@ -1058,22 +1092,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Integrated System Type</t>
+          <t>Organization performs maintenance activities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IntegratedSystemType</t>
+          <t>MaintenanceEnabledFlag</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IntegratedSystemType</t>
+          <t>MaintenanceEnabledFlag</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1087,10 +1121,102 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
+          <t>Inventory Organization parent field</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Centang jika organization menjalankan maintenance activities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Additional Usages</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Organization represents a contract manufacturer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ContractManufacturingFlag</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ContractManufacturingFlag</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Inventory Organization parent field</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Centang jika organization merepresentasikan contract manufacturer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Additional Usages</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Integrated System Type</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IntegratedSystemType</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>IntegratedSystemType</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>Ambil dari existing IO/current value jika tersedia.</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Integrated System Type. Kosongkan jika tidak ingin di-update. Isi dengan value/code yang memang valid di instance Oracle.</t>
         </is>

--- a/sample_data/organization_usage_update_template.xlsx
+++ b/sample_data/organization_usage_update_template.xlsx
@@ -432,16 +432,16 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,12 +467,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>DefSupplySubinv</t>
+          <t>DefaultSupplySubinventory</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>DefCompltnSubinv</t>
+          <t>DefaultCompletionSubinventory</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -517,12 +517,8 @@
           <t>IO Test 01</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>300000000000001</v>
-      </c>
-      <c r="D2" t="n">
-        <v>300000047225452</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>RAW</t>
@@ -538,7 +534,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -546,11 +542,7 @@
       <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Oracle Inventory Management</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -867,12 +859,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DefSupplySubinv</t>
+          <t>DefaultSupplySubinventory</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DefSupplySubinv</t>
+          <t>DefaultSupplySubinventory</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -896,7 +888,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kode/nama subinventory default supply untuk create plantParameters. Wajib diisi jika ManufacturingPlantFlag atau MaintenanceEnabledFlag dicentang.</t>
+          <t>Kode/nama subinventory default supply untuk create plantParameters. Wajib diisi jika ManufacturingPlantFlag atau MaintenanceEnabledFlag dicentang. Dikirim ke REST plantParameters sebagai DefaultSupplySubinventory.</t>
         </is>
       </c>
     </row>
@@ -913,12 +905,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DefCompltnSubinv</t>
+          <t>DefaultCompletionSubinventory</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DefCompltnSubinv</t>
+          <t>DefaultCompletionSubinventory</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -942,7 +934,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Kode/nama subinventory default completion untuk create plantParameters. Wajib diisi jika ManufacturingPlantFlag atau MaintenanceEnabledFlag dicentang.</t>
+          <t>Kode/nama subinventory default completion untuk create plantParameters. Wajib diisi jika ManufacturingPlantFlag atau MaintenanceEnabledFlag dicentang. Dikirim ke REST plantParameters sebagai DefaultCompletionSubinventory.</t>
         </is>
       </c>
     </row>
